--- a/XLS/S3/e_codes.xlsx
+++ b/XLS/S3/e_codes.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" url="C:\Users\Mohammed Al-Emara\Documents\"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC9CC82-5416-4B56-8453-467413DCE1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Al-Emara\Documents\GitHub\Statistical-notebook\XLS\S3\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CC6A0A-9396-4284-832D-45FE7ED8ECD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" r:id="rId1" name="e_codes"/>
+    <sheet name="e_codes" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="e_codes">'e_codes'!$A$1:$F$66</definedName>
+    <definedName name="e_codes">e_codes!$A$1:$F$66</definedName>
   </definedNames>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
@@ -24,9 +28,6 @@
     <t>code_key</t>
   </si>
   <si>
-    <t>q5</t>
-  </si>
-  <si>
     <t>q7</t>
   </si>
   <si>
@@ -232,6 +233,9 @@
   </si>
   <si>
     <t>حكاية</t>
+  </si>
+  <si>
+    <t>q3</t>
   </si>
 </sst>
 </file>
@@ -572,56 +576,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>code_key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>q3</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>q7</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>q8</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>q9</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>q18</t>
-        </is>
-      </c>
-    </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1400135</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>اطفال النجف</t>
-        </is>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -633,17 +623,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1400136</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>الحوراء</t>
-        </is>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -655,17 +643,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1400137</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>الاجيال</t>
-        </is>
+      <c r="C4" t="s">
+        <v>7</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -677,17 +663,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1400138</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>البراعم</t>
-        </is>
+      <c r="C5" t="s">
+        <v>8</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -699,17 +683,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1400139</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>الزيتون</t>
-        </is>
+      <c r="C6" t="s">
+        <v>9</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -721,17 +703,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1400140</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>النرجس</t>
-        </is>
+      <c r="C7" t="s">
+        <v>10</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -743,17 +723,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1400141</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>البيادر</t>
-        </is>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -765,17 +743,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1400142</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>الربيع</t>
-        </is>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -787,17 +763,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1400143</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>الهديل</t>
-        </is>
+      <c r="C10" t="s">
+        <v>13</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -809,17 +783,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1400144</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>الشهيدة احلام رزاق كاظم دبش</t>
-        </is>
+      <c r="C11" t="s">
+        <v>14</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -831,17 +803,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1400145</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>الغدير</t>
-        </is>
+      <c r="C12" t="s">
+        <v>15</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -853,17 +823,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1400146</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>العبير</t>
-        </is>
+      <c r="C13" t="s">
+        <v>16</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -875,17 +843,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1400147</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>المباهج</t>
-        </is>
+      <c r="C14" t="s">
+        <v>17</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -897,17 +863,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1400148</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>اطفال الثورة</t>
-        </is>
+      <c r="C15" t="s">
+        <v>18</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -919,17 +883,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1400149</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>الحسين</t>
-        </is>
+      <c r="C16" t="s">
+        <v>19</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -941,17 +903,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1400150</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>الشموع</t>
-        </is>
+      <c r="C17" t="s">
+        <v>20</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -963,17 +923,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1400151</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>قتيبة</t>
-        </is>
+      <c r="C18" t="s">
+        <v>21</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -985,17 +943,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1400152</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>الاستبرق</t>
-        </is>
+      <c r="C19" t="s">
+        <v>22</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1007,17 +963,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1400153</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>الافاق الرحبة</t>
-        </is>
+      <c r="C20" t="s">
+        <v>23</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1029,17 +983,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1400154</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>الزنابق</t>
-        </is>
+      <c r="C21" t="s">
+        <v>24</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1051,17 +1003,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1400760</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>العسل</t>
-        </is>
+      <c r="C22" t="s">
+        <v>25</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1073,17 +1023,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1400774</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>جنة الزهراء</t>
-        </is>
+      <c r="C23" t="s">
+        <v>26</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1095,17 +1043,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1400779</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>زهرة الوادي</t>
-        </is>
+      <c r="C24" t="s">
+        <v>27</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1117,17 +1063,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1400794</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>طيور الجنة</t>
-        </is>
+      <c r="C25" t="s">
+        <v>28</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1139,17 +1083,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1400827</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ندى القلوب</t>
-        </is>
+      <c r="C26" t="s">
+        <v>29</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1161,17 +1103,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1400960</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>الابتسامة</t>
-        </is>
+      <c r="C27" t="s">
+        <v>30</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1183,17 +1123,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1401004</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>حمائم السلام</t>
-        </is>
+      <c r="C28" t="s">
+        <v>31</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1205,17 +1143,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1401121</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>العصافير</t>
-        </is>
+      <c r="C29" t="s">
+        <v>32</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1227,17 +1163,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="30">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1401154</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>النوارس البيضاء</t>
-        </is>
+      <c r="C30" t="s">
+        <v>33</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1249,17 +1183,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="31">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1401194</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>تنمية الذكاء ( تعليق )</t>
-        </is>
+      <c r="C31" t="s">
+        <v>34</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1271,17 +1203,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="32">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1401195</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>السنافر</t>
-        </is>
+      <c r="C32" t="s">
+        <v>35</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1293,17 +1223,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="33">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1401275</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>سما</t>
-        </is>
+      <c r="C33" t="s">
+        <v>36</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1315,17 +1243,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="34">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1401277</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>الوارث</t>
-        </is>
+      <c r="C34" t="s">
+        <v>37</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1337,17 +1263,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1401318</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>كفيلة الايتام (( لم يصدر كتابها )) / تعليق</t>
-        </is>
+      <c r="C35" t="s">
+        <v>38</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1359,17 +1283,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="36">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1401322</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>احباب المرتضى</t>
-        </is>
+      <c r="C36" t="s">
+        <v>39</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1381,17 +1303,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="37">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1401324</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>شموس الغري (( تعليق ))</t>
-        </is>
+      <c r="C37" t="s">
+        <v>40</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1403,17 +1323,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="38">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1401402</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>الملاك</t>
-        </is>
+      <c r="C38" t="s">
+        <v>41</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1425,17 +1343,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="39">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1401418</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>المبدعون الصغار</t>
-        </is>
+      <c r="C39" t="s">
+        <v>42</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1447,17 +1363,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="40">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1401513</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>الفرقان</t>
-        </is>
+      <c r="C40" t="s">
+        <v>43</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1469,17 +1383,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="41">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1401566</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>نيوتن</t>
-        </is>
+      <c r="C41" t="s">
+        <v>44</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1491,17 +1403,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="42">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1401660</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>العبقري الصغير</t>
-        </is>
+      <c r="C42" t="s">
+        <v>45</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1513,17 +1423,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="43">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1400155</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>اطفال الكوفة</t>
-        </is>
+      <c r="C43" t="s">
+        <v>46</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -1535,17 +1443,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="44">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1400156</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>الينابيع</t>
-        </is>
+      <c r="C44" t="s">
+        <v>47</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1557,17 +1463,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1400157</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>الورود</t>
-        </is>
+      <c r="C45" t="s">
+        <v>48</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1579,17 +1483,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="46">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1400158</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>الاصيل</t>
-        </is>
+      <c r="C46" t="s">
+        <v>49</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1601,17 +1503,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="47">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1400159</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>الاريج</t>
-        </is>
+      <c r="C47" t="s">
+        <v>50</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1623,17 +1523,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="48">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1400160</v>
       </c>
       <c r="B48">
         <v>2</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>السندس</t>
-        </is>
+      <c r="C48" t="s">
+        <v>51</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -1645,17 +1543,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="49">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1400161</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>الياسمين</t>
-        </is>
+      <c r="C49" t="s">
+        <v>52</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1667,17 +1563,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="50">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1400162</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>الازاهير</t>
-        </is>
+      <c r="C50" t="s">
+        <v>53</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1689,17 +1583,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="51">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1400998</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>السندباد</t>
-        </is>
+      <c r="C51" t="s">
+        <v>54</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -1711,17 +1603,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="52">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1401072</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>البنفسج</t>
-        </is>
+      <c r="C52" t="s">
+        <v>55</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -1733,17 +1623,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="53">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1401185</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>انوار الحسن المجتبى</t>
-        </is>
+      <c r="C53" t="s">
+        <v>56</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -1755,17 +1643,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="54">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1401438</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>لولو كاتي</t>
-        </is>
+      <c r="C54" t="s">
+        <v>57</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -1777,17 +1663,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="55">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1401612</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>كادي</t>
-        </is>
+      <c r="C55" t="s">
+        <v>58</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -1799,17 +1683,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="56">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1400163</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>السدير</t>
-        </is>
+      <c r="C56" t="s">
+        <v>59</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -1821,17 +1703,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="57">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1400164</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>الشروق</t>
-        </is>
+      <c r="C57" t="s">
+        <v>60</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -1843,17 +1723,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="58">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1400165</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>الرياحين</t>
-        </is>
+      <c r="C58" t="s">
+        <v>61</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -1865,17 +1743,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="59">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1400166</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>المشخاب</t>
-        </is>
+      <c r="C59" t="s">
+        <v>62</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -1887,17 +1763,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="60">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1400167</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>النسيم</t>
-        </is>
+      <c r="C60" t="s">
+        <v>63</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -1909,17 +1783,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="61">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1400168</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>القادسية</t>
-        </is>
+      <c r="C61" t="s">
+        <v>64</v>
       </c>
       <c r="D61">
         <v>4</v>
@@ -1931,17 +1803,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="62">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1401070</v>
       </c>
       <c r="B62">
         <v>3</v>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>اطفال المناذرة</t>
-        </is>
+      <c r="C62" t="s">
+        <v>65</v>
       </c>
       <c r="D62">
         <v>3</v>
@@ -1953,17 +1823,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="63">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1401071</v>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>اطفال الدسم</t>
-        </is>
+      <c r="C63" t="s">
+        <v>66</v>
       </c>
       <c r="D63">
         <v>3</v>
@@ -1975,17 +1843,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="64">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1401122</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>رقية بنت الحسين</t>
-        </is>
+      <c r="C64" t="s">
+        <v>67</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -1997,17 +1863,15 @@
         <v>1</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="65">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1401466</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ساندي بيل ( غلق )</t>
-        </is>
+      <c r="C65" t="s">
+        <v>68</v>
       </c>
       <c r="D65">
         <v>4</v>
@@ -2019,17 +1883,15 @@
         <v>2</v>
       </c>
     </row>
-    <row spans="1:6" x14ac:dyDescent="0.3" outlineLevel="0" r="66">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1401720</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>حكاية</t>
-        </is>
+      <c r="C66" t="s">
+        <v>69</v>
       </c>
       <c r="D66">
         <v>4</v>

--- a/XLS/S3/e_codes.xlsx
+++ b/XLS/S3/e_codes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Al-Emara\Documents\GitHub\Statistical-notebook\XLS\S3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CC6A0A-9396-4284-832D-45FE7ED8ECD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C757C395-091A-4215-A79D-60436554E161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
